--- a/Bid_Config_Files_Local/BidMasterFiles_Local.xlsx
+++ b/Bid_Config_Files_Local/BidMasterFiles_Local.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -455,9 +455,33 @@
         <v>C:\Users\siddesh.gp\Downloads\QuadgenWirless_BMS - Production\QuadgenWirless_BMS - Production - Copy (2)\Bid_Config_Files_Local\New_Bids_Local\testing2\testing2_MasterFileChecklist.xlsx</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>testing3</v>
+      </c>
+      <c r="B8" t="str">
+        <v>C:\Users\siddesh.gp\Downloads\QuadgenWirless_BMS - Production\QuadgenWirless_BMS - Production - Copy (2)\Bid_Config_Files_Local\New_Bids_Local\testing3\testing3_MasterFileChecklist.xlsx</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>tirupathi</v>
+      </c>
+      <c r="B9" t="str">
+        <v>C:\Users\siddesh.gp\Downloads\QuadgenWirless_BMS - Production\QuadgenWirless_BMS - Production - Copy (2)\Bid_Config_Files_Local\New_Bids_Local\tirupathi\tirupathi_MasterFileChecklist.xlsx</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>hgvhgvhvh</v>
+      </c>
+      <c r="B10" t="str">
+        <v>C:\Users\siddesh.gp\Downloads\QuadgenWirless_BMS - Production\QuadgenWirless_BMS - Production - Copy (2)\Bid_Config_Files_Local\New_Bids_Local\hgvhgvhvh\hgvhgvhvh_MasterFileChecklist.xlsx</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Bid_Config_Files_Local/BidMasterFiles_Local.xlsx
+++ b/Bid_Config_Files_Local/BidMasterFiles_Local.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -441,47 +441,39 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>testing</v>
+        <v>testing3</v>
       </c>
       <c r="B6" t="str">
-        <v>C:\Users\siddesh.gp\Downloads\QuadgenWirless_BMS - Production\QuadgenWirless_BMS - Production - Copy (2)\Bid_Config_Files_Local\New_Bids_Local\testing\testing_MasterFileChecklist.xlsx</v>
+        <v>C:\Users\siddesh.gp\Downloads\QuadgenWirless_BMS - Production\QuadgenWirless_BMS - Production - Copy (2)\Bid_Config_Files_Local\New_Bids_Local\testing3\testing3_MasterFileChecklist.xlsx</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>testing2</v>
+        <v>tirupathi</v>
       </c>
       <c r="B7" t="str">
-        <v>C:\Users\siddesh.gp\Downloads\QuadgenWirless_BMS - Production\QuadgenWirless_BMS - Production - Copy (2)\Bid_Config_Files_Local\New_Bids_Local\testing2\testing2_MasterFileChecklist.xlsx</v>
+        <v>C:\Users\siddesh.gp\Downloads\QuadgenWirless_BMS - Production\QuadgenWirless_BMS - Production - Copy (2)\Bid_Config_Files_Local\New_Bids_Local\tirupathi\tirupathi_MasterFileChecklist.xlsx</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>testing3</v>
+        <v>hgvhgvhvh</v>
       </c>
       <c r="B8" t="str">
-        <v>C:\Users\siddesh.gp\Downloads\QuadgenWirless_BMS - Production\QuadgenWirless_BMS - Production - Copy (2)\Bid_Config_Files_Local\New_Bids_Local\testing3\testing3_MasterFileChecklist.xlsx</v>
+        <v>C:\Users\siddesh.gp\Downloads\QuadgenWirless_BMS - Production\QuadgenWirless_BMS - Production - Copy (2)\Bid_Config_Files_Local\New_Bids_Local\hgvhgvhvh\hgvhgvhvh_MasterFileChecklist.xlsx</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>tirupathi</v>
+        <v>qg</v>
       </c>
       <c r="B9" t="str">
-        <v>C:\Users\siddesh.gp\Downloads\QuadgenWirless_BMS - Production\QuadgenWirless_BMS - Production - Copy (2)\Bid_Config_Files_Local\New_Bids_Local\tirupathi\tirupathi_MasterFileChecklist.xlsx</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>hgvhgvhvh</v>
-      </c>
-      <c r="B10" t="str">
-        <v>C:\Users\siddesh.gp\Downloads\QuadgenWirless_BMS - Production\QuadgenWirless_BMS - Production - Copy (2)\Bid_Config_Files_Local\New_Bids_Local\hgvhgvhvh\hgvhgvhvh_MasterFileChecklist.xlsx</v>
+        <v>C:\Users\siddesh.gp\Downloads\QuadgenWirless_BMS - Production\QuadgenWirless_BMS - Production - Copy (2)\Bid_Config_Files_Local\New_Bids_Local\qg\qg_MasterFileChecklist.xlsx</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B9"/>
   </ignoredErrors>
 </worksheet>
 </file>